--- a/data_input/output/income density distance privacy odin 2023.xlsx
+++ b/data_input/output/income density distance privacy odin 2023.xlsx
@@ -1,14 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6bba444eb789f06d/Documents/GitHub/Housing-Fooprints/housing-footprints/data_input/output/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_3341719F4D781C2CFCD71747EC012D16710CA428" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4D58DBD-7EC4-417E-8E9B-AD8749347C9A}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="10276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AF$251</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1044,11 +1054,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1067,28 +1082,360 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF251"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1185,7 +1532,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1283,7 +1630,7 @@
         <v>94841126.5234375</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1381,7 +1728,7 @@
         <v>138949565.31054688</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1479,7 +1826,7 @@
         <v>96213772.2890625</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1577,7 +1924,7 @@
         <v>70078986.64453125</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1675,7 +2022,7 @@
         <v>1504749.0625</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1773,7 +2120,7 @@
         <v>49571224.515625</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -1871,7 +2218,7 @@
         <v>40330841.9296875</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -1969,7 +2316,7 @@
         <v>70100254.41015625</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -2067,7 +2414,7 @@
         <v>25315190.722167969</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -2165,7 +2512,7 @@
         <v>23030652.1328125</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -2263,7 +2610,7 @@
         <v>30923567.4765625</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -2361,7 +2708,7 @@
         <v>29505684.421875</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -2459,7 +2806,7 @@
         <v>52187375.21484375</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -2557,7 +2904,7 @@
         <v>39685145.1953125</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -2655,7 +3002,7 @@
         <v>40832505.69921875</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -2753,7 +3100,7 @@
         <v>14430076.14453125</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -2851,7 +3198,7 @@
         <v>14218125.8125</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -2949,7 +3296,7 @@
         <v>16087811.96875</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -3047,7 +3394,7 @@
         <v>42580677.78515625</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -3145,7 +3492,7 @@
         <v>47079306.83203125</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1</v>
       </c>
@@ -3201,7 +3548,7 @@
         <v>4537566.75</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1</v>
       </c>
@@ -3257,7 +3604,7 @@
         <v>3650230.84375</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1</v>
       </c>
@@ -3355,7 +3702,7 @@
         <v>18695224.5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -3453,7 +3800,7 @@
         <v>36541103.1953125</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1</v>
       </c>
@@ -3551,7 +3898,7 @@
         <v>65802967.1953125</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>2</v>
       </c>
@@ -3649,7 +3996,7 @@
         <v>69934361.001953125</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -3747,7 +4094,7 @@
         <v>85668506.875</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>2</v>
       </c>
@@ -3845,7 +4192,7 @@
         <v>76886050.9375</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>2</v>
       </c>
@@ -3943,7 +4290,7 @@
         <v>40134177.75</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>2</v>
       </c>
@@ -4041,7 +4388,7 @@
         <v>11033004.0625</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -4139,7 +4486,7 @@
         <v>81520809.20703125</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>2</v>
       </c>
@@ -4237,7 +4584,7 @@
         <v>61529465.111328125</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>2</v>
       </c>
@@ -4335,7 +4682,7 @@
         <v>98470174.1015625</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>2</v>
       </c>
@@ -4433,7 +4780,7 @@
         <v>58820072.8046875</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>2</v>
       </c>
@@ -4531,7 +4878,7 @@
         <v>30352938.607421875</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>2</v>
       </c>
@@ -4629,7 +4976,7 @@
         <v>21541540.76171875</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>2</v>
       </c>
@@ -4727,7 +5074,7 @@
         <v>26424634.01171875</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>2</v>
       </c>
@@ -4825,7 +5172,7 @@
         <v>40806140.064453125</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>2</v>
       </c>
@@ -4923,7 +5270,7 @@
         <v>39705206.3359375</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>2</v>
       </c>
@@ -5021,7 +5368,7 @@
         <v>18440196.203125</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>2</v>
       </c>
@@ -5119,7 +5466,7 @@
         <v>13139783.890625</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>2</v>
       </c>
@@ -5217,7 +5564,7 @@
         <v>22767363.40625</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -5315,7 +5662,7 @@
         <v>14567407.9609375</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>2</v>
       </c>
@@ -5413,7 +5760,7 @@
         <v>46948461.828125</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>2</v>
       </c>
@@ -5511,7 +5858,7 @@
         <v>60417780.30078125</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>2</v>
       </c>
@@ -5609,7 +5956,7 @@
         <v>509463.5546875</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>2</v>
       </c>
@@ -5665,7 +6012,7 @@
         <v>4005801.9375</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>2</v>
       </c>
@@ -5763,7 +6110,7 @@
         <v>37643120.375</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>2</v>
       </c>
@@ -5861,7 +6208,7 @@
         <v>41540526.706054688</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>2</v>
       </c>
@@ -5959,7 +6306,7 @@
         <v>99370441.3359375</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>3</v>
       </c>
@@ -6057,7 +6404,7 @@
         <v>83459723.81640625</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -6155,7 +6502,7 @@
         <v>84536396.73828125</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>3</v>
       </c>
@@ -6253,7 +6600,7 @@
         <v>55161911.345703125</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -6351,7 +6698,7 @@
         <v>41302407.19140625</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>3</v>
       </c>
@@ -6449,7 +6796,7 @@
         <v>8633376.41015625</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>3</v>
       </c>
@@ -6547,7 +6894,7 @@
         <v>60526017.71484375</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>3</v>
       </c>
@@ -6645,7 +6992,7 @@
         <v>73291583.877929688</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>3</v>
       </c>
@@ -6743,7 +7090,7 @@
         <v>80978242.4296875</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>3</v>
       </c>
@@ -6841,7 +7188,7 @@
         <v>61555551.06640625</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>3</v>
       </c>
@@ -6939,7 +7286,7 @@
         <v>23418175.75390625</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>3</v>
       </c>
@@ -7037,7 +7384,7 @@
         <v>59152007.719726563</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>3</v>
       </c>
@@ -7135,7 +7482,7 @@
         <v>49058175.51171875</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>3</v>
       </c>
@@ -7233,7 +7580,7 @@
         <v>41759623.6484375</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>3</v>
       </c>
@@ -7331,7 +7678,7 @@
         <v>39396713.494140625</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>3</v>
       </c>
@@ -7429,7 +7776,7 @@
         <v>52165131.46875</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>3</v>
       </c>
@@ -7527,7 +7874,7 @@
         <v>27598345.52734375</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>3</v>
       </c>
@@ -7625,7 +7972,7 @@
         <v>16442259.369140625</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>3</v>
       </c>
@@ -7723,7 +8070,7 @@
         <v>31886673.67578125</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>3</v>
       </c>
@@ -7821,7 +8168,7 @@
         <v>45137762.362792969</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>3</v>
       </c>
@@ -7919,7 +8266,7 @@
         <v>100031309.20703125</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>3</v>
       </c>
@@ -8017,7 +8364,7 @@
         <v>7589100.8515625</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>3</v>
       </c>
@@ -8115,7 +8462,7 @@
         <v>4231224.00390625</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -8213,7 +8560,7 @@
         <v>13921218.067382813</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>3</v>
       </c>
@@ -8311,7 +8658,7 @@
         <v>84721622.25</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>3</v>
       </c>
@@ -8409,7 +8756,7 @@
         <v>107036597.6640625</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>4</v>
       </c>
@@ -8507,7 +8854,7 @@
         <v>96925333.55078125</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>4</v>
       </c>
@@ -8605,7 +8952,7 @@
         <v>100542600.15039063</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>4</v>
       </c>
@@ -8703,7 +9050,7 @@
         <v>89968385.7109375</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>4</v>
       </c>
@@ -8801,7 +9148,7 @@
         <v>38338456.9609375</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -8899,7 +9246,7 @@
         <v>6242545.25</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -8997,7 +9344,7 @@
         <v>67913840.484375</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -9095,7 +9442,7 @@
         <v>73998414.88671875</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -9193,7 +9540,7 @@
         <v>74932184.1953125</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>4</v>
       </c>
@@ -9291,7 +9638,7 @@
         <v>63788395.546875</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>4</v>
       </c>
@@ -9389,7 +9736,7 @@
         <v>48936029.984375</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>4</v>
       </c>
@@ -9487,7 +9834,7 @@
         <v>55519395.9296875</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>4</v>
       </c>
@@ -9585,7 +9932,7 @@
         <v>57636058.03125</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -9683,7 +10030,7 @@
         <v>58258213.926757813</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>4</v>
       </c>
@@ -9781,7 +10128,7 @@
         <v>69723076.796875</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -9879,7 +10226,7 @@
         <v>76502136.130859375</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>4</v>
       </c>
@@ -9977,7 +10324,7 @@
         <v>42053871.875</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>4</v>
       </c>
@@ -10075,7 +10422,7 @@
         <v>16402889.609375</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>4</v>
       </c>
@@ -10173,7 +10520,7 @@
         <v>26923846.796875</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -10271,7 +10618,7 @@
         <v>58266993.9453125</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -10369,7 +10716,7 @@
         <v>78928884.28515625</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -10467,7 +10814,7 @@
         <v>2772550.7421875</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>4</v>
       </c>
@@ -10565,7 +10912,7 @@
         <v>5745849.46875</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>4</v>
       </c>
@@ -10663,7 +11010,7 @@
         <v>21052813.1640625</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>4</v>
       </c>
@@ -10761,7 +11108,7 @@
         <v>77324976.1953125</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>4</v>
       </c>
@@ -10859,7 +11206,7 @@
         <v>107553231.0390625</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -10957,7 +11304,7 @@
         <v>98677070.302246094</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>5</v>
       </c>
@@ -11055,7 +11402,7 @@
         <v>88046924.9609375</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>5</v>
       </c>
@@ -11153,7 +11500,7 @@
         <v>83956486.6171875</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>5</v>
       </c>
@@ -11251,7 +11598,7 @@
         <v>36675396.91796875</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>5</v>
       </c>
@@ -11349,7 +11696,7 @@
         <v>7151568.5625</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>5</v>
       </c>
@@ -11447,7 +11794,7 @@
         <v>68573389.484375</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>5</v>
       </c>
@@ -11545,7 +11892,7 @@
         <v>121034397.9140625</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>5</v>
       </c>
@@ -11643,7 +11990,7 @@
         <v>84731623.9375</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>5</v>
       </c>
@@ -11741,7 +12088,7 @@
         <v>88456812.60546875</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -11839,7 +12186,7 @@
         <v>44188140.05078125</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>5</v>
       </c>
@@ -11937,7 +12284,7 @@
         <v>47913971.0234375</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -12035,7 +12382,7 @@
         <v>66632707.75</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>5</v>
       </c>
@@ -12133,7 +12480,7 @@
         <v>54022393.328125</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>5</v>
       </c>
@@ -12231,7 +12578,7 @@
         <v>82064816.9765625</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>5</v>
       </c>
@@ -12329,7 +12676,7 @@
         <v>61572762.4375</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>5</v>
       </c>
@@ -12427,7 +12774,7 @@
         <v>45625663.15234375</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -12525,7 +12872,7 @@
         <v>33390263.84765625</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>5</v>
       </c>
@@ -12623,7 +12970,7 @@
         <v>45495329.724609375</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -12721,7 +13068,7 @@
         <v>86201695.4296875</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -12819,7 +13166,7 @@
         <v>92713795.591796875</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -12917,7 +13264,7 @@
         <v>8785924.171875</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>5</v>
       </c>
@@ -13015,7 +13362,7 @@
         <v>15010481.9453125</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -13113,7 +13460,7 @@
         <v>46791385.19140625</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -13211,7 +13558,7 @@
         <v>81282419.310546875</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -13309,7 +13656,7 @@
         <v>112438571.33203125</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>6</v>
       </c>
@@ -13407,7 +13754,7 @@
         <v>100819268.8203125</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>6</v>
       </c>
@@ -13505,7 +13852,7 @@
         <v>132326531.97070313</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>6</v>
       </c>
@@ -13603,7 +13950,7 @@
         <v>98104108.8359375</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>6</v>
       </c>
@@ -13701,7 +14048,7 @@
         <v>36873446.259765625</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -13799,7 +14146,7 @@
         <v>8397261.96875</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>6</v>
       </c>
@@ -13897,7 +14244,7 @@
         <v>84614626.236328125</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>6</v>
       </c>
@@ -13995,7 +14342,7 @@
         <v>99048637.0625</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>6</v>
       </c>
@@ -14093,7 +14440,7 @@
         <v>126658568.90820313</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -14191,7 +14538,7 @@
         <v>91313902.6171875</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>6</v>
       </c>
@@ -14289,7 +14636,7 @@
         <v>41063272.552734375</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>6</v>
       </c>
@@ -14387,7 +14734,7 @@
         <v>48565332.2109375</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>6</v>
       </c>
@@ -14485,7 +14832,7 @@
         <v>72318784.07421875</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>6</v>
       </c>
@@ -14583,7 +14930,7 @@
         <v>90317857.4296875</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -14681,7 +15028,7 @@
         <v>76322302.95703125</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>6</v>
       </c>
@@ -14779,7 +15126,7 @@
         <v>75219287.62109375</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>6</v>
       </c>
@@ -14877,7 +15224,7 @@
         <v>47219430.9375</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>6</v>
       </c>
@@ -14975,7 +15322,7 @@
         <v>49501812.578125</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>6</v>
       </c>
@@ -15073,7 +15420,7 @@
         <v>47513988.81640625</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>6</v>
       </c>
@@ -15171,7 +15518,7 @@
         <v>113289792.046875</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>6</v>
       </c>
@@ -15269,7 +15616,7 @@
         <v>130474236.75878906</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>6</v>
       </c>
@@ -15367,7 +15714,7 @@
         <v>9793597.453125</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>6</v>
       </c>
@@ -15465,7 +15812,7 @@
         <v>13090721.734375</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>6</v>
       </c>
@@ -15563,7 +15910,7 @@
         <v>23702501.8125</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>6</v>
       </c>
@@ -15661,7 +16008,7 @@
         <v>119587572.40625</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -15759,7 +16106,7 @@
         <v>181303508.22070313</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>7</v>
       </c>
@@ -15857,7 +16204,7 @@
         <v>87398790.59375</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>7</v>
       </c>
@@ -15955,7 +16302,7 @@
         <v>123206991.00976563</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>7</v>
       </c>
@@ -16053,7 +16400,7 @@
         <v>95154702.615234375</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>7</v>
       </c>
@@ -16151,7 +16498,7 @@
         <v>56504805.77734375</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>7</v>
       </c>
@@ -16249,7 +16596,7 @@
         <v>10579661.21875</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>7</v>
       </c>
@@ -16347,7 +16694,7 @@
         <v>105925326.63671875</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>7</v>
       </c>
@@ -16445,7 +16792,7 @@
         <v>107835143.16064453</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>7</v>
       </c>
@@ -16543,7 +16890,7 @@
         <v>147836697.3125</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>7</v>
       </c>
@@ -16641,7 +16988,7 @@
         <v>80779746.119140625</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>7</v>
       </c>
@@ -16739,7 +17086,7 @@
         <v>47294626.033203125</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>7</v>
       </c>
@@ -16837,7 +17184,7 @@
         <v>72860453.5078125</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>7</v>
       </c>
@@ -16935,7 +17282,7 @@
         <v>85525984.126953125</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>7</v>
       </c>
@@ -17033,7 +17380,7 @@
         <v>126724399.41992188</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>7</v>
       </c>
@@ -17131,7 +17478,7 @@
         <v>79952862.2109375</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>7</v>
       </c>
@@ -17229,7 +17576,7 @@
         <v>93261317.883789063</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>7</v>
       </c>
@@ -17327,7 +17674,7 @@
         <v>41430295.50390625</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -17425,7 +17772,7 @@
         <v>39137872.93359375</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>7</v>
       </c>
@@ -17523,7 +17870,7 @@
         <v>59092843.18359375</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>7</v>
       </c>
@@ -17621,7 +17968,7 @@
         <v>79990428.72265625</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>7</v>
       </c>
@@ -17719,7 +18066,7 @@
         <v>106970588.359375</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>7</v>
       </c>
@@ -17817,7 +18164,7 @@
         <v>2955326.59375</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>7</v>
       </c>
@@ -17915,7 +18262,7 @@
         <v>17932627.375</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>7</v>
       </c>
@@ -18013,7 +18360,7 @@
         <v>34907295.2421875</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>7</v>
       </c>
@@ -18111,7 +18458,7 @@
         <v>140741372.99023438</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>7</v>
       </c>
@@ -18209,7 +18556,7 @@
         <v>152816593.44921875</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>8</v>
       </c>
@@ -18307,7 +18654,7 @@
         <v>120779675.43554688</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>8</v>
       </c>
@@ -18405,7 +18752,7 @@
         <v>130190015.68945313</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>8</v>
       </c>
@@ -18503,7 +18850,7 @@
         <v>108263952.55859375</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>8</v>
       </c>
@@ -18601,7 +18948,7 @@
         <v>51096691.6328125</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>8</v>
       </c>
@@ -18699,7 +19046,7 @@
         <v>5456131.1796875</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>8</v>
       </c>
@@ -18797,7 +19144,7 @@
         <v>82921621.060546875</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>8</v>
       </c>
@@ -18895,7 +19242,7 @@
         <v>124849264.69238281</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>8</v>
       </c>
@@ -18993,7 +19340,7 @@
         <v>111413342.9765625</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>8</v>
       </c>
@@ -19091,7 +19438,7 @@
         <v>97805264.306640625</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>8</v>
       </c>
@@ -19189,7 +19536,7 @@
         <v>45063727.94140625</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>8</v>
       </c>
@@ -19287,7 +19634,7 @@
         <v>63345635.794921875</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>8</v>
       </c>
@@ -19385,7 +19732,7 @@
         <v>74292934.67578125</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>8</v>
       </c>
@@ -19483,7 +19830,7 @@
         <v>110526849.1796875</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>8</v>
       </c>
@@ -19581,7 +19928,7 @@
         <v>96698322.1484375</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>8</v>
       </c>
@@ -19679,7 +20026,7 @@
         <v>72482459.130859375</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>8</v>
       </c>
@@ -19777,7 +20124,7 @@
         <v>37444472.96484375</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>8</v>
       </c>
@@ -19875,7 +20222,7 @@
         <v>58486555.515625</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>8</v>
       </c>
@@ -19973,7 +20320,7 @@
         <v>60089694.6015625</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>8</v>
       </c>
@@ -20071,7 +20418,7 @@
         <v>125912750.28515625</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>8</v>
       </c>
@@ -20169,7 +20516,7 @@
         <v>112764346.25</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>8</v>
       </c>
@@ -20267,7 +20614,7 @@
         <v>12523227.671875</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>8</v>
       </c>
@@ -20365,7 +20712,7 @@
         <v>21549556.890625</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>8</v>
       </c>
@@ -20463,7 +20810,7 @@
         <v>32630867.412109375</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>8</v>
       </c>
@@ -20561,7 +20908,7 @@
         <v>81103612.944335938</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>8</v>
       </c>
@@ -20659,7 +21006,7 @@
         <v>146345699.37695313</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -20757,7 +21104,7 @@
         <v>160197899.75976563</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>9</v>
       </c>
@@ -20855,7 +21202,7 @@
         <v>159898663.55078125</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>9</v>
       </c>
@@ -20953,7 +21300,7 @@
         <v>129405510.27929688</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>9</v>
       </c>
@@ -21051,7 +21398,7 @@
         <v>80332746.75</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>9</v>
       </c>
@@ -21149,7 +21496,7 @@
         <v>773094.4609375</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -21247,7 +21594,7 @@
         <v>81811907.861328125</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>9</v>
       </c>
@@ -21345,7 +21692,7 @@
         <v>130748494.88378906</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>9</v>
       </c>
@@ -21443,7 +21790,7 @@
         <v>114714072.55859375</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>9</v>
       </c>
@@ -21541,7 +21888,7 @@
         <v>102508013.48242188</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>9</v>
       </c>
@@ -21639,7 +21986,7 @@
         <v>47781643.423828125</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>9</v>
       </c>
@@ -21737,7 +22084,7 @@
         <v>67381650.9921875</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>9</v>
       </c>
@@ -21835,7 +22182,7 @@
         <v>63154577.46484375</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>9</v>
       </c>
@@ -21933,7 +22280,7 @@
         <v>104067282.72460938</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>9</v>
       </c>
@@ -22031,7 +22378,7 @@
         <v>98070259.3125</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>9</v>
       </c>
@@ -22129,7 +22476,7 @@
         <v>46483126.01953125</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>9</v>
       </c>
@@ -22227,7 +22574,7 @@
         <v>26475413.6796875</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>9</v>
       </c>
@@ -22325,7 +22672,7 @@
         <v>41090352.703125</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>9</v>
       </c>
@@ -22423,7 +22770,7 @@
         <v>63968289.434570313</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>9</v>
       </c>
@@ -22521,7 +22868,7 @@
         <v>102850302.42382813</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>9</v>
       </c>
@@ -22619,7 +22966,7 @@
         <v>107871092.26855469</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>9</v>
       </c>
@@ -22717,7 +23064,7 @@
         <v>7232991.21875</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>9</v>
       </c>
@@ -22815,7 +23162,7 @@
         <v>5968894.09375</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>9</v>
       </c>
@@ -22913,7 +23260,7 @@
         <v>47725738</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>9</v>
       </c>
@@ -23011,7 +23358,7 @@
         <v>119709732.04492188</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>9</v>
       </c>
@@ -23109,7 +23456,7 @@
         <v>164235309.60742188</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>10</v>
       </c>
@@ -23207,7 +23554,7 @@
         <v>133494062.39453125</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>10</v>
       </c>
@@ -23305,7 +23652,7 @@
         <v>184916276.01953125</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>10</v>
       </c>
@@ -23403,7 +23750,7 @@
         <v>109606146.859375</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>10</v>
       </c>
@@ -23501,7 +23848,7 @@
         <v>68866905.35546875</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>10</v>
       </c>
@@ -23599,7 +23946,7 @@
         <v>938487.0078125</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>10</v>
       </c>
@@ -23697,7 +24044,7 @@
         <v>73554096.89453125</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>10</v>
       </c>
@@ -23795,7 +24142,7 @@
         <v>114254037.69921875</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>10</v>
       </c>
@@ -23893,7 +24240,7 @@
         <v>122268157.640625</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>10</v>
       </c>
@@ -23991,7 +24338,7 @@
         <v>106065147.69140625</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>10</v>
       </c>
@@ -24089,7 +24436,7 @@
         <v>41039505.2734375</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>10</v>
       </c>
@@ -24187,7 +24534,7 @@
         <v>38664577.609375</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>10</v>
       </c>
@@ -24285,7 +24632,7 @@
         <v>56031357.177734375</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>10</v>
       </c>
@@ -24383,7 +24730,7 @@
         <v>90314139.802734375</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>10</v>
       </c>
@@ -24481,7 +24828,7 @@
         <v>99597743.373046875</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>10</v>
       </c>
@@ -24579,7 +24926,7 @@
         <v>55386984.2890625</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>10</v>
       </c>
@@ -24677,7 +25024,7 @@
         <v>44286184.57421875</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>10</v>
       </c>
@@ -24775,7 +25122,7 @@
         <v>40950438.044921875</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>10</v>
       </c>
@@ -24873,7 +25220,7 @@
         <v>73716600.01171875</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>10</v>
       </c>
@@ -24971,7 +25318,7 @@
         <v>115900786.51757813</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>10</v>
       </c>
@@ -25069,7 +25416,7 @@
         <v>97926779.5625</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>10</v>
       </c>
@@ -25167,7 +25514,7 @@
         <v>3581870.8984375</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>10</v>
       </c>
@@ -25265,7 +25612,7 @@
         <v>9729193.578125</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>10</v>
       </c>
@@ -25363,7 +25710,7 @@
         <v>56590208.45703125</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>10</v>
       </c>
@@ -25461,7 +25808,7 @@
         <v>159719646.97460938</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>10</v>
       </c>
@@ -25560,5 +25907,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AF251" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>